--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -802,26 +802,22 @@
       <c r="C18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SORT</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -831,12 +827,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -848,12 +844,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -865,12 +861,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -882,12 +878,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -899,12 +895,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -916,12 +912,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -933,10 +929,27 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -815,77 +815,57 @@
       <c r="C19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>シッソウ迷宮リドレール</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>テストプレイお願いします</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>国旗なぞ</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>雨の出会いと、隠されたメッセージ</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -895,12 +875,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -912,12 +892,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -929,12 +909,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
+          <t>NAZOxNAZO劇団</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -946,10 +926,90 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>MICHI</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>미치</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SCRAP - Mystery For You</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -60,6 +60,13 @@
       <name val="Arial"/>
       <charset val="129"/>
       <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -489,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -899,7 +906,11 @@
           <t>謎解き死霊使いと14通の手紙</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>나조토키 사령술사와 14통의 편지, 네크로맨서, 수수께끼 풀이</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -912,7 +923,11 @@
           <t>魔術解析機関-Institution of Witch Craft Analyzation-</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>마술해석기관, 마법</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -925,7 +940,11 @@
           <t>STREET NAZO ART</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>스트릿 나조 아트, 스트리트</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -938,29 +957,29 @@
           <t>ULTIMATE PUZZLE TOWER</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>얼티밋 퍼즐 타워, 얼티미트</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AXIDENTZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -970,12 +989,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -987,12 +1006,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1023,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1040,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1057,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1074,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1072,31 +1091,61 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>SCRAP - Mystery For You</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4CE Dimension</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -974,46 +974,35 @@
           <t>AXIDENTZ</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>タンブルダイス</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>はじみまして</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1023,12 +1012,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1029,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1046,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1063,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1080,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1108,44 +1097,77 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>SCRAP - Mystery For You</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>4CE Dimension</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1000,26 +1000,21 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Answersheet</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1029,12 +1024,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1041,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1058,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1075,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1092,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1109,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1131,29 +1126,29 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1164,6 +1159,23 @@
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>SCRAP - Mystery For You</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>4CE Dimension</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,26 +1012,21 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1041,12 +1036,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1053,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1070,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1087,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1104,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1121,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1143,29 +1138,29 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1176,6 +1171,23 @@
         </is>
       </c>
       <c r="B42" t="inlineStr">
+        <is>
+          <t>SCRAP - Mystery For You</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>4CE Dimension</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1024,26 +1024,21 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>アナビナゾ</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1053,12 +1048,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1065,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1082,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1099,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1116,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1133,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1155,29 +1150,29 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1184,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>SCRAP - Mystery For You</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>4CE Dimension</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AnotherVision</t>
         </is>
       </c>
     </row>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -63,10 +63,15 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
+      <name val="Malgun Gothic"/>
       <charset val="129"/>
       <family val="2"/>
-      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -121,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -131,6 +136,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -782,7 +788,7 @@
           <t>나조 이름</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>金のエンジェル缶</t>
         </is>
@@ -974,6 +980,11 @@
           <t>AXIDENTZ</t>
         </is>
       </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>액시덴츠, 액시덴트, 엑시덴츠, 엑시덴트</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -986,6 +997,11 @@
           <t>タンブルダイス</t>
         </is>
       </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>텀블다이스, 텀블 다이트, 탐브루다이스, 탐부루다이스,</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -998,6 +1014,11 @@
           <t>はじみまして</t>
         </is>
       </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>하지미마시떼, 하지미마시테</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1008,6 +1029,11 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>Answersheet</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>앤서시트, 안사시트, 안-사시트, 답안지</t>
         </is>
       </c>
     </row>
@@ -1204,6 +1230,11 @@
           <t>4CE Dimension</t>
         </is>
       </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>포스 디멘션, 포스 디멘젼</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monbbang/Library/Mobile Documents/com~apple~CloudDocs/MacBook Air M2/나조토키/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4376728C-DE45-7F4A-8A28-ED749C6A2733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA3F71F-58F3-F34C-B418-B388ED472D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,9 +88,6 @@
     <t>히라메키 트럼프 실버, 히라메키트럼프 실버, 히라메키트럼프실버, 히라메키 트럼프실버, 히라메키, 트럼프, 실버</t>
   </si>
   <si>
-    <t>アルティメットナゾトキショウ (얼티밋 나조토키쇼)</t>
-  </si>
-  <si>
     <t>얼티밋 나조토키쇼, 얼티밋나조토키쇼, 궁극의 나조토키쇼, 궁극의나조토키쇼, 얼티밋, 나조토키, 쇼</t>
   </si>
   <si>
@@ -295,6 +292,10 @@
   </si>
   <si>
     <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>アルティメットナゾトキショウ</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -406,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -417,7 +418,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -842,11 +842,11 @@
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -854,10 +854,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -865,10 +865,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -876,10 +876,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -887,10 +887,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -898,10 +898,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -909,10 +909,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -920,10 +920,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -931,10 +931,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -942,10 +942,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -953,10 +953,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -964,10 +964,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -975,10 +975,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -986,10 +986,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -997,10 +997,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1008,10 +1008,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1019,10 +1019,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1030,10 +1030,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1041,10 +1041,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1052,10 +1052,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1063,10 +1063,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1074,10 +1074,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1085,10 +1085,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>89</v>
+        <v>64</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1098,123 +1098,123 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1078,26 +1078,21 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>馬崎 春のぱずる祭り 2026</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1107,12 +1102,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1119,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1136,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1153,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1170,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1187,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1209,29 +1204,29 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1238,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1260,10 +1255,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>4CE Dimension</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>포스 디멘션, 포스 디멘젼</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>AnotherVision</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1113,60 +1113,45 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FouRe:</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Collection : lie</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>馬崎 春のぱずる祭り2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1176,12 +1161,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1178,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1195,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1212,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>MICHI</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1244,61 +1229,112 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>SCRAP - Mystery For You</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>4CE Dimension</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>AnotherVision</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1149,26 +1149,21 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>パズバコ</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1178,12 +1173,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1190,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1207,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1224,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1241,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1258,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1280,29 +1275,29 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1309,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1331,10 +1326,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>4CE Dimension</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>포스 디멘션, 포스 디멘젼</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>AnotherVision</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1161,194 +1161,350 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>パズバコ2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>みんなで競技謎解き-ANSWER COMBO-</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MAZE-MAZE RIDDLE</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ミニパズバコ</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>パズバコ3</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RIDDLE BOX!!!</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>時解き</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UNIVERSE</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>カナロス -図鑑編-</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>SCRAP</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>カナロス -絵日記編-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>브랜드</t>
+          <t>나조 이름</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
+          <t>母の日に思い出して</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>スケルトンフリーク</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>MICHI</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>미치</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SCRAP</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SCRAP - Mystery For You</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>4CE Dimension</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>AnotherVision</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>xeoxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>リドラ</t>
         </is>
       </c>
     </row>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1293,43 +1293,33 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1339,12 +1329,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1346,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1363,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1380,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1397,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1424,46 +1414,46 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>4CE Dimension</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1465,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1482,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>4CE Dimension</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1503,6 +1498,35 @@
         </is>
       </c>
       <c r="B65" t="inlineStr">
+        <is>
+          <t>AnotherVision</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>xeoxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>リドラ</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
+          <t>タンブルなななぞ</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
+          <t>KORON -コロン-</t>
         </is>
       </c>
     </row>
@@ -1324,116 +1324,86 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XI</t>
+          <t>封筒RUSH</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>あめもようの ばけもの</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>プロポーズは謎解きで</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>まほうのキッチン</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>COUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>イツツボシ</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>メモリアート</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>時解き</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>토키토키, tokitoki,토키,toki</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1443,12 +1413,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1460,87 +1430,201 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>MICHI</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>미치</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>SCRAP - Mystery For You</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>4CE Dimension</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>AnotherVision</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>xeoxy</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>リドラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ねずみの巣</t>
         </is>
       </c>
     </row>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1317,26 +1317,21 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1346,12 +1341,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1358,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1375,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1392,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1409,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1426,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1448,29 +1443,29 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1477,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1494,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1511,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1527,6 +1527,18 @@
         </is>
       </c>
       <c r="B67" t="inlineStr">
+        <is>
+          <t>xeoxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>リドラ</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -66,6 +66,13 @@
       <name val="Malgun Gothic"/>
       <charset val="129"/>
       <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -497,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1108,7 +1115,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Collection:lie</t>
+          <t>FouRe:</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>포리, 포레</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1132,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FouRe:</t>
+          <t>Collection : lie</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>콜렉션라이, 컬렉션라이, 콜렉션 라이, 컬렉션 라이, 콜렉션:라이, 컬렉션:라이, 콜렉션 : 라이, 컬렉션 : 라이</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1149,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Collection : lie</t>
+          <t>馬崎 春のぱずる祭り2026</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>마사키 봄의 퍼즐 축제 2026</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1166,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>馬崎 春のぱずる祭り2026</t>
+          <t>パズバコ</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>파즈바코, 파즈바코 1</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1183,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>パズバコ</t>
+          <t>パズバコ2</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>파즈바코 2</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1200,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>パズバコ2</t>
+          <t>みんなで競技謎解き-ANSWER COMBO-</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>민나데 쿄기 나조토키 앤서콤보, 민나데 쿄기 나조토키 안사콤보, 앤서콤보, 안사콤보</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1217,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>みんなで競技謎解き-ANSWER COMBO-</t>
+          <t>MAZE-MAZE RIDDLE</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>메이즈 메이즈 리들, 메이즈-메이즈 리들, 마제 마제 리들, 마제-마제 리들, 메이즈 메이즈 리도루, 메이즈-메이즈 리도루, 마제 마제 리도루, 마제-마제 리도루</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1234,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MAZE-MAZE RIDDLE</t>
+          <t>ミニパズバコ</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>미니파즈바코, 미니 파즈바코</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1251,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ミニパズバコ</t>
+          <t>パズバコ3</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>파즈바코 3</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1268,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>パズバコ3</t>
+          <t>RIDDLE BOX!!!</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>리들 박스!!!, 리들 복꾸스!!!</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1285,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RIDDLE BOX!!!</t>
+          <t>UNIVERSE</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>유니버스, 우주</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1302,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIVERSE</t>
+          <t>カナロス -図鑑編-</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>카나로스 도감편</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1319,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>カナロス -図鑑編-</t>
+          <t>カナロス -絵日記編-</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>카나로스 그림일기편</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1336,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>カナロス -絵日記編-</t>
+          <t>母の日に思い出して</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>어머니날에 떠올려 줘, 하하노히</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1353,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>母の日に思い出して</t>
+          <t>スケルトンフリーク</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>스켈레톤 프릭, 스켈레톤 프리크, 스케루톤 프리쿠, 스케루톤 프리크</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1370,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>スケルトンフリーク</t>
+          <t>タンブルなななぞ</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>탐브루 나나나조, 텀블 나나나조, 텀브루 나나나조, 일곱나조, 칠나조, 7나조</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1387,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>タンブルなななぞ</t>
+          <t>KORON -コロン-</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>코론, 데굴</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1404,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KORON -コロン-</t>
+          <t>封筒RUSH</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>봉투러쉬, 봉투 러쉬</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1421,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>封筒RUSH</t>
+          <t>あめもようの ばけもの</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>비 오는 날의 괴물</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1438,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>あめもようの ばけもの</t>
+          <t>プロポーズは謎解きで</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>프로포즈는 나조토키로, 프러포즈는 나조토키로</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1455,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>プロポーズは謎解きで</t>
+          <t>まほうのキッチン</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>마법의 키친, 마호오노 킷친, 마호노 킷친, 마호노 키친, 마법의 주방</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1472,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>まほうのキッチン</t>
+          <t>COUST</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>쿠스트, 코스트</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1489,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COUST</t>
+          <t>イツツボシ</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>이츠츠보시, 다섯개의 별, 다섯개의별</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1506,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>イツツボシ</t>
+          <t>メモリアート</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>메모리아트, 메모리 아트</t>
         </is>
       </c>
     </row>
@@ -1396,31 +1523,36 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>メモリアート</t>
+          <t>CONTROLLER</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>컨트롤러, 콘토로라, 콘토로-라</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ドキドキ謎解き肝試し</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>도키도키 나조토키 담력시험, 두근두근 나조토키 담력시험</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1430,12 +1562,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1579,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1596,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1613,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1630,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1647,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1532,29 +1664,29 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1698,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1715,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1732,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1749,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>xeoxy</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1624,11 +1766,85 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>リドラ</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>리도라, 리들러</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>일레븐, 엑스아이</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1550,26 +1550,21 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Paradox5</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1579,12 +1574,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1591,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1608,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1625,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1642,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1659,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1681,29 +1676,29 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1710,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1727,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1744,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>제옥시</t>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1761,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>xeoxy</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1783,29 +1778,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>リドラ</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1812,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
@@ -1834,10 +1829,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>일레븐, 엑스아이</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1562,26 +1562,21 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Premium One vol.1 -THE CARDS-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1591,12 +1586,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1603,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1620,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1637,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1654,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1671,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1693,29 +1688,29 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1722,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1739,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1756,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>제옥시</t>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1773,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>xeoxy</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1795,29 +1790,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>リドラ</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1824,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1841,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>일레븐, 엑스아이</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1574,77 +1574,57 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Premium One vol.2 -THE NUMBERS-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>解錠</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>サイフアーカイブ</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TUMBLEWEED HITS</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1654,12 +1634,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1651,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1668,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
+          <t>NAZOxNAZO劇団</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1705,80 +1685,80 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
+          <t>MICHI</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>미치</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>4CE Dimension</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>AnotherVision</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>xeoxy</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1770,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1807,61 +1787,129 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>AnotherVision</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>xeoxy</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>リドラ</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>리도라, 리들러</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>일레븐, 엑스아이</t>
         </is>
